--- a/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête. Papa dit : c'est une vache. C'est le nom de l'animal. La vache fait meuh. Estelle dit : meuh. C'est le cri. Plus loin, un coq chante. Papa dit : c'est un coq. Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse. Papa dit : canard. Le cri, c'est coin-coin. Estelle dit : coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit. Estelle reste près de papa.</t>
+          <t>Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête. C'est une vache. C'est le nom de l'animal. La vache fait meuh. Meuh. C'est le cri. Plus loin, un coq chante. C'est un coq. Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse. Canard. Le cri, c'est coin-coin. Coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit. Estelle reste près de papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,20 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête.
+papa|C'est une vache. C'est le nom de l'animal.
+narrateur|La vache fait meuh.
+enfant-f|Meuh. C'est le cri. Plus loin, un coq chante.
+papa|C'est un coq.
+narrateur|Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse.
+papa|Canard.
+narrateur|Le cri, c'est coin-coin.
+enfant-f|Coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit.
+narrateur|Estelle reste près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1499,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La vache fait un bruit. Quel est ce cri ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Estelle a dit le nom de l'animal. Elle a dit le cri. Vache, coq, canard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1839,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Estelle donne la main à papa. Ils quittent la ferme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2006,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2046,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,7 @@
 narrateur|Estelle reste près de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1506,6 +1512,7 @@
           <t>narrateur|La vache fait un bruit. Quel est ce cri ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Estelle a dit le nom de l'animal. Elle a dit le cri. Vache, coq, canard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1844,6 +1852,7 @@
           <t>narrateur|Estelle donne la main à papa. Ils quittent la ferme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2011,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2053,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2254,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Estelle nomme les cris à la ferme</t>
+          <t>La poule du matin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut la poule du matin. Elle glousse près du seau. Le soir, un hibou hulule loin sur les toits.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête. C'est une vache. C'est le nom de l'animal. La vache fait meuh. Meuh. C'est le cri. Plus loin, un coq chante. C'est un coq. Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse. Canard. Le cri, c'est coin-coin. Coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit. Estelle reste près de papa.</t>
+          <t>Le seau de lait fume encore dans la cuisine. Une goutte blanche sèche sur le bois. La fenêtre donne sur la cour grise. Un râteau s'appuie contre le mur froid. Tu sens le lait, Raphaël ? Oui. Il est chaud. Je veux la poule. Celle qui a pondu ? Oui. En ce moment, Raphaël ouvre la porte. L'air de la cour pique un peu. La terre est encore mouillée de rosée. Un cot cot arrive près du seau vide. La poule ! Tu as entendu ? Cot cot. La poule glousse. La poule brune gratte sous le râteau. Un œuf sale brille dans la paille. Elle a pondu. On la regarde d'ici ? Oui. Raphaël s'accroupit près du seau. La poule tourne l'œil, tout rond. Elle glousse encore, plus doux. Cot cot. C'est son cri. Le lait de la cuisine sent encore. La poule picore un grain près du bois. Raphaël ne la prend pas. On la laisse. Elle a son œuf. Raphaël touche le seau vide, tout froid. La poule glousse une dernière fois. Je l'ai eue. Le matin, c'est elle. Un grain reste collé au bec de la poule. Raphaël rit tout bas. Cot cot. Tu as son cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête. Papa dit : c'est une vache. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. La vache fait meuh. Estelle dit : meuh. C'est le cri. Plus loin, un coq chante. Papa dit : c'est un coq. Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse. Papa dit : canard. Le cri, c'est coin-coin. Estelle dit : coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit. Estelle reste près de papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le seau de lait fume encore dans la cuisine. Une goutte blanche sèche sur le bois. La fenêtre donne sur la cour grise. Un râteau s'appuie contre le mur froid. Tu sens le lait, Raphaël ? Oui. Il est chaud. Je veux la poule. Celle qui a pondu ? Oui. En ce moment, Raphaël ouvre la porte. L'air de la cour pique un peu. La terre est encore mouillée de rosée. Un cot cot arrive près du seau vide. La poule ! Tu as entendu ? Cot cot. La poule glousse. La poule brune gratte sous le râteau. Un œuf sale brille dans la paille. Elle a pondu. On la regarde d'ici ? Oui. Raphaël s'accroupit près du seau. La poule tourne l'œil, tout rond. Elle glousse encore, plus doux. Cot cot. C'est son cri. Le lait de la cuisine sent encore. La poule picore un grain près du bois. Raphaël ne la prend pas. On la laisse. Elle a son œuf. Raphaël touche le seau vide, tout froid. La poule glousse une dernière fois. Je l'ai eue. Le matin, c'est elle. Un grain reste collé au bec de la poule. Raphaël rit tout bas. Cot cot. Tu as son cri.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,19 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Estelle arrive à la ferme avec papa. L'herbe est tiède. Une vache lève la tête.
-papa|C'est une vache. C'est le nom de l'animal.
-narrateur|La vache fait meuh.
-enfant-f|Meuh. C'est le cri. Plus loin, un coq chante.
-papa|C'est un coq.
-narrateur|Le nom de l'animal. Le cri, c'est cocorico. Estelle répète : cocorico. Ils vont vers l'étang. Un canard glisse.
-papa|Canard.
-narrateur|Le cri, c'est coin-coin.
-enfant-f|Coin-coin. Même leçon, autre animal. On nomme l'animal. On dit le cri. Papa sourit.
-narrateur|Estelle reste près de papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le seau de lait fume encore dans la cuisine.
+narrateur|Une goutte blanche sèche sur le bois.
+narrateur|La fenêtre donne sur la cour grise.
+narrateur|Un râteau s'appuie contre le mur froid.
+papa|Tu sens le lait, Raphaël ?
+enfant-m|Oui.
+enfant-m|Il est chaud.
+enfant-m|Je veux la poule.
+papa|Celle qui a pondu ?
+enfant-m|Oui.
+narrateur|En ce moment, Raphaël ouvre la porte.
+narrateur|L'air de la cour pique un peu.
+narrateur|La terre est encore mouillée de rosée.
+narrateur|Un cot cot arrive près du seau vide.
+enfant-m|La poule !
+papa|Tu as entendu ?
+enfant-m|Cot cot.
+papa|La poule glousse.
+narrateur|La poule brune gratte sous le râteau.
+narrateur|Un œuf sale brille dans la paille.
+enfant-m|Elle a pondu.
+papa|On la regarde d'ici ?
+enfant-m|Oui.
+narrateur|Raphaël s'accroupit près du seau.
+narrateur|La poule tourne l'œil, tout rond.
+narrateur|Elle glousse encore, plus doux.
+enfant-m|Cot cot.
+papa|C'est son cri.
+narrateur|Le lait de la cuisine sent encore.
+narrateur|La poule picore un grain près du bois.
+narrateur|Raphaël ne la prend pas.
+papa|On la laisse.
+papa|Elle a son œuf.
+narrateur|Raphaël touche le seau vide, tout froid.
+narrateur|La poule glousse une dernière fois.
+enfant-m|Je l'ai eue.
+papa|Le matin, c'est elle.
+narrateur|Un grain reste collé au bec de la poule.
+narrateur|Raphaël rit tout bas.
+enfant-m|Cot cot.
+papa|Tu as son cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1349,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La vache fait un bruit. Quel est ce cri ?</t>
+          <t>Raphaël entend cot cot. Quel est le cri de la poule ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vache fait un bruit. Quel est ce &lt;emphasis level="moderate"&gt;cri&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël entend cot cot. Quel est le cri de la poule ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,12 +1406,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>meuh</t>
+          <t>cot cot</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>meuh | vache | cocorico | coin-coin | le cri</t>
+          <t>cot cot | glousse | elle glousse | le cri | la poule</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1384,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On dit le nom de l'animal. On dit le cri. Quel cri ?</t>
+          <t>La poule glousse. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,14 +1468,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1509,10 +1551,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La vache fait un bruit. Quel est ce cri ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël entend cot cot.
+narrateur|Quel est le cri de la poule ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1537,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Estelle a dit le nom de l'animal. Elle a dit le cri. Vache, coq, canard.</t>
+          <t>Plus tard, la cour devient bleue. Le seau de lait a disparu de la table. Papa ferme le petit volet de bois. La poule dort ? Oui. Elle est rentrée. Un cri rond arrive des toits. Hou hou, tout loin. Ce n'est pas la poule. Tu entends, Raphaël ? Hou hou. Un hibou hulule. Raphaël lève le nez vers les tuiles noires. Rien ne bouge, seulement le cri. Merci d'avoir écouté le soir aussi. Le hou hou revient, plus mince.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Estelle a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Elle a dit le cri. Vache, coq, canard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Plus tard, la cour devient bleue. Le seau de lait a disparu de la table. Papa ferme le petit volet de bois. La poule dort ? Oui. Elle est rentrée. Un cri rond arrive des toits. Hou hou, tout loin. Ce n'est pas la poule. Tu entends, Raphaël ? Hou hou. Un hibou hulule. Raphaël lève le nez vers les tuiles noires. Rien ne bouge, seulement le cri. Merci d'avoir écouté le soir aussi. Le hou hou revient, plus mince.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1605,7 +1647,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1723,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Estelle a dit le nom de l'animal. Elle a dit le cri. Vache, coq, canard.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Plus tard, la cour devient bleue.
+narrateur|Le seau de lait a disparu de la table.
+narrateur|Papa ferme le petit volet de bois.
+enfant-m|La poule dort ?
+papa|Oui.
+papa|Elle est rentrée.
+narrateur|Un cri rond arrive des toits.
+narrateur|Hou hou, tout loin.
+enfant-m|Ce n'est pas la poule.
+papa|Tu entends, Raphaël ?
+enfant-m|Hou hou.
+papa|Un hibou hulule.
+narrateur|Raphaël lève le nez vers les tuiles noires.
+narrateur|Rien ne bouge, seulement le cri.
+papa|Merci d'avoir écouté le soir aussi.
+narrateur|Le hou hou revient, plus mince.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Estelle donne la main à papa. Ils quittent la ferme.</t>
+          <t>La poule ne glousse plus. Le hibou reste loin, sur les toits. Deux cris. Le matin, la poule. Le soir, le hibou. Raphaël pose l'oreille vers la cour. L'air est froid maintenant. Hou hou. C'est son cri, à lui. Une étoile perce au-dessus du râteau. Le bois du volet sent la poussière. On rentre ? Encore un peu. Raphaël compte deux silences. Celui de la poule, celui du hibou. Le hou hou est loin. Oui. La rosée du matin a disparu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Estelle donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils quittent la ferme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poule ne glousse plus. Le hibou reste loin, sur les toits. Deux cris. Le matin, la poule. Le soir, le hibou. Raphaël pose l'oreille vers la cour. L'air est froid maintenant. Hou hou. C'est son cri, à lui. Une étoile perce au-dessus du râteau. Le bois du volet sent la poussière. On rentre ? Encore un peu. Raphaël compte deux silences. Celui de la poule, celui du hibou. Le hou hou est loin. Oui. La rosée du matin a disparu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1777,7 +1833,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1849,10 +1905,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Estelle donne la main à papa. Ils quittent la ferme.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La poule ne glousse plus.
+narrateur|Le hibou reste loin, sur les toits.
+enfant-m|Deux cris.
+papa|Le matin, la poule.
+papa|Le soir, le hibou.
+narrateur|Raphaël pose l'oreille vers la cour.
+narrateur|L'air est froid maintenant.
+enfant-m|Hou hou.
+papa|C'est son cri, à lui.
+narrateur|Une étoile perce au-dessus du râteau.
+narrateur|Le bois du volet sent la poussière.
+papa|On rentre ?
+enfant-m|Encore un peu.
+narrateur|Raphaël compte deux silences.
+narrateur|Celui de la poule, celui du hibou.
+enfant-m|Le hou hou est loin.
+papa|Oui.
+narrateur|La rosée du matin a disparu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1877,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le hou hou s'efface dans les toits noirs. Raphaël prend la main de papa. La poule, puis le hibou. Oui. Le seau vide brille encore sous la fenêtre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le hou hou s'efface dans les toits noirs. Raphaël prend la main de papa. La poule, puis le hibou. Oui. Le seau vide brille encore sous la fenêtre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1945,7 +2017,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2017,10 +2089,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le hou hou s'efface dans les toits noirs.
+narrateur|Raphaël prend la main de papa.
+enfant-m|La poule, puis le hibou.
+papa|Oui.
+narrateur|Le seau vide brille encore sous la fenêtre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2039,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>ferme, cuisine puis cour, matin et soir</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estelle, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
